--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -1261,10 +1261,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <v>45771</v>
+        <v>45801</v>
       </c>
       <c r="E2" s="4">
-        <v>45771</v>
+        <v>45801</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
-    <sheet name="LeaveTemplate" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -48,6 +48,18 @@
   </si>
   <si>
     <t>LOP</t>
+  </si>
+  <si>
+    <t>20-10-2025</t>
+  </si>
+  <si>
+    <t>20-Oct-25</t>
+  </si>
+  <si>
+    <t>25-Oct-20</t>
+  </si>
+  <si>
+    <t>2025-Oct-20</t>
   </si>
 </sst>
 </file>
@@ -701,7 +713,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1227,10 +1239,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="16.1428571428571" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="17.0"/>
+    <col min="5" max="5" customWidth="true" width="16.1454545454545"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1260,11 +1272,11 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
-        <v>45801</v>
+      <c r="D2" t="s" s="0">
+        <v>10</v>
       </c>
-      <c r="E2" s="4">
-        <v>45801</v>
+      <c r="E2" t="s" s="0">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>2025-Oct-20</t>
+  </si>
+  <si>
+    <t>2025-Nov-17</t>
   </si>
 </sst>
 </file>
@@ -1273,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>2025-Nov-17</t>
+  </si>
+  <si>
+    <t>2025-Nov-18</t>
   </si>
 </sst>
 </file>
@@ -1276,10 +1279,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="14">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>2025-Nov-18</t>
+  </si>
+  <si>
+    <t>2025-Dec-04</t>
   </si>
 </sst>
 </file>
@@ -1279,10 +1282,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>2025-Dec-04</t>
+  </si>
+  <si>
+    <t>2026-Feb-05</t>
   </si>
 </sst>
 </file>
@@ -1282,10 +1285,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="16">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>2026-Feb-05</t>
+  </si>
+  <si>
+    <t>2026-Apr-01</t>
   </si>
 </sst>
 </file>
@@ -1285,10 +1288,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="18">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>2026-Apr-01</t>
+  </si>
+  <si>
+    <t>2026-Jul-08</t>
+  </si>
+  <si>
+    <t>2026-Jul-09</t>
   </si>
 </sst>
 </file>
@@ -1288,10 +1294,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>2026-Jul-09</t>
+  </si>
+  <si>
+    <t>2026-Sep-08</t>
   </si>
 </sst>
 </file>
@@ -1294,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LOPLeaveMigrationData.xlsx
+++ b/testdata/LOPLeaveMigrationData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>2026-Sep-08</t>
+  </si>
+  <si>
+    <t>2026-Oct-05</t>
   </si>
 </sst>
 </file>
@@ -1297,10 +1300,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
